--- a/tame_output/MOZAIC/data/universe_last2023-07-27.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-27.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>570.4281690284049</v>
+        <v>570.579593934408</v>
       </c>
       <c r="E2" t="n">
-        <v>13473.55583632316</v>
+        <v>13447.19293857713</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6277613466389955</v>
+        <v>0.6285781031267437</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4995414711377312</v>
+        <v>0.4995396631555027</v>
       </c>
       <c r="H2" t="n">
-        <v>1.256675136919537</v>
+        <v>1.258314703493469</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>224.9917288657117</v>
+        <v>225.7562054365478</v>
       </c>
       <c r="E3" t="n">
-        <v>5782.64078380912</v>
+        <v>5803.426972112772</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2657931850846043</v>
+        <v>0.2664633371450289</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5988666133212764</v>
+        <v>0.5988653315633613</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4438270211968104</v>
+        <v>0.4449470074505999</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907162640934128</v>
+        <v>0.8907157771458715</v>
       </c>
       <c r="N3" t="n">
-        <v>1.0678197173358</v>
+        <v>1.067820712853246</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.65361621749965</v>
+        <v>37.53499833942598</v>
       </c>
       <c r="E4" t="n">
-        <v>1671.991431845816</v>
+        <v>1659.685841905225</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7931060397412857</v>
+        <v>0.7879944128851699</v>
       </c>
       <c r="G4" t="n">
-        <v>1.110592577962568</v>
+        <v>1.110611271801176</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7141287052325475</v>
+        <v>0.709514150353625</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4735968304823422</v>
+        <v>0.4735931938735952</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052911830688161</v>
+        <v>1.052925279329825</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.76444341648621</v>
+        <v>36.81571636330064</v>
       </c>
       <c r="E5" t="n">
-        <v>417.3450538207687</v>
+        <v>412.2310482377949</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3433073896050072</v>
+        <v>-0.3418150205253144</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5623945353887836</v>
+        <v>0.562399024362785</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6104387009515991</v>
+        <v>-0.6077802515973443</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7366410656049479</v>
+        <v>0.7366252814563273</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8293263598228244</v>
+        <v>0.8293182106803783</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.90874961975522</v>
+        <v>10.94851230730431</v>
       </c>
       <c r="E6" t="n">
-        <v>833.8165776885227</v>
+        <v>793.9444033352812</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4873451099147998</v>
+        <v>-0.4815045118533897</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8157128798530381</v>
+        <v>0.8157119226341868</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5974468737119877</v>
+        <v>-0.5902874513571682</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6679634484419387</v>
+        <v>0.6679165529237313</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090733041491388</v>
+        <v>1.09065913225596</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.74078455932773</v>
+        <v>10.76474957424572</v>
       </c>
       <c r="E7" t="n">
-        <v>210.7873084044637</v>
+        <v>209.3455376386929</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3147863187455656</v>
+        <v>-0.3126648121047451</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7156724311797238</v>
+        <v>0.7156787418713688</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.439846925815862</v>
+        <v>-0.436878719196247</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7510930660059315</v>
+        <v>0.7510756209958092</v>
       </c>
       <c r="N7" t="n">
-        <v>1.076060010325931</v>
+        <v>1.076048400419426</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.28944344015598</v>
+        <v>10.01560502590497</v>
       </c>
       <c r="E8" t="n">
-        <v>708.9998750266561</v>
+        <v>708.8261935717513</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2883504130845878</v>
+        <v>-0.3107394264693449</v>
       </c>
       <c r="G8" t="n">
-        <v>1.173678043176902</v>
+        <v>1.17383821136373</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2456810151309326</v>
+        <v>-0.2647208307423705</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7375848085507967</v>
+        <v>0.7375794500115088</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732963417041757</v>
+        <v>1.733193590416938</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.382233219465058</v>
+        <v>7.381431692834557</v>
       </c>
       <c r="E9" t="n">
-        <v>229.9703947277219</v>
+        <v>228.7459746205541</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4312547739605306</v>
+        <v>0.430547595904863</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4806852256427324</v>
+        <v>0.4806872300078137</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8971666923689874</v>
+        <v>0.8956917700889712</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6788599166689622</v>
+        <v>0.6788591717529852</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6532349185756708</v>
+        <v>0.6532392898975083</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.719147402189463</v>
+        <v>6.738347546305466</v>
       </c>
       <c r="E10" t="n">
-        <v>334.6790077327482</v>
+        <v>328.6844861229803</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2638458824212839</v>
+        <v>-0.2607929625978147</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9600989600653748</v>
+        <v>0.9600913652639883</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.274811132389226</v>
+        <v>-0.2716334840967001</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7134948345066306</v>
+        <v>0.7134856992717395</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371308866632537</v>
+        <v>1.371285424630831</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.664021633736999</v>
+        <v>6.704634841271496</v>
       </c>
       <c r="E11" t="n">
-        <v>414.210253384435</v>
+        <v>427.8507574637721</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9771059497414514</v>
+        <v>0.9868503205903085</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8228976792475819</v>
+        <v>0.8229096335003813</v>
       </c>
       <c r="H11" t="n">
-        <v>1.187396652564229</v>
+        <v>1.199220765459481</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6643122207689128</v>
+        <v>0.664285765062345</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094325529212814</v>
+        <v>1.094301805814382</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.637382265686126</v>
+        <v>6.36140417359132</v>
       </c>
       <c r="E12" t="n">
-        <v>102.1199805301153</v>
+        <v>102.5917651306411</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2727593319942977</v>
+        <v>-0.2691755910505214</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6596012632407994</v>
+        <v>0.6596166175198216</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4135215427789773</v>
+        <v>-0.408078850503539</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7889991111536515</v>
+        <v>0.788959819089503</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041805016163168</v>
+        <v>1.041781154952792</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.719632952239362</v>
+        <v>4.73801618598084</v>
       </c>
       <c r="E13" t="n">
-        <v>241.3875198757208</v>
+        <v>247.6345177734999</v>
       </c>
       <c r="F13" t="n">
-        <v>1.759693719783808</v>
+        <v>1.768943632799012</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8623576357464243</v>
+        <v>0.8623607194671514</v>
       </c>
       <c r="H13" t="n">
-        <v>2.040561417723962</v>
+        <v>2.051280389825772</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6039504532567208</v>
+        <v>0.6039373501251989</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042598693142033</v>
+        <v>1.042583574799999</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.590474254245241</v>
+        <v>4.587434979129345</v>
       </c>
       <c r="E14" t="n">
-        <v>123.344292190886</v>
+        <v>119.6905854483058</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3982428409023409</v>
+        <v>-0.3994740487726847</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8517864571304206</v>
+        <v>0.8517890897900607</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4675383572591413</v>
+        <v>-0.4689823496930942</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,45 +1192,45 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601553479390911</v>
+        <v>0.7601631113817611</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296168722919218</v>
+        <v>1.296190658106541</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.204859371653895</v>
+        <v>4.267937873960314</v>
       </c>
       <c r="E15" t="n">
-        <v>281.69574282245</v>
+        <v>382.9380166865365</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5591324262581778</v>
+        <v>0.01193470458209456</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9622628101541174</v>
+        <v>0.7947230630423694</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5810599977033575</v>
+        <v>0.01501743832172929</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3858131487889274</v>
+        <v>0.4268646717284502</v>
       </c>
       <c r="J15" t="n">
         <v>269</v>
@@ -1246,45 +1246,45 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5144086631442107</v>
+        <v>0.7153531921637969</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9909013652808277</v>
+        <v>1.138063144860987</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.1629151613304</v>
+        <v>4.211268284920711</v>
       </c>
       <c r="E16" t="n">
-        <v>349.4246889472748</v>
+        <v>287.6809616178132</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.01877719373637643</v>
+        <v>0.5659872612567243</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7942795356352841</v>
+        <v>0.9622222486421166</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.02364053572317959</v>
+        <v>0.5882084539776988</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4268646717284502</v>
+        <v>0.3858131487889274</v>
       </c>
       <c r="J16" t="n">
         <v>269</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.715877354967172</v>
+        <v>0.5144065392530186</v>
       </c>
       <c r="N16" t="n">
-        <v>1.138257313812425</v>
+        <v>0.9908590917277523</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.368240545221205</v>
+        <v>3.394368641127036</v>
       </c>
       <c r="E17" t="n">
-        <v>73.01643069872351</v>
+        <v>79.34149493661023</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2116633107959228</v>
+        <v>-0.2054303509205885</v>
       </c>
       <c r="G17" t="n">
-        <v>0.754580304581335</v>
+        <v>0.7546053101825909</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2805046852016106</v>
+        <v>-0.2722354960249097</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244555475459784</v>
+        <v>0.7243996268447978</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094323333111536</v>
+        <v>1.094279084183969</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.110771871042802</v>
+        <v>3.113087790752991</v>
       </c>
       <c r="E18" t="n">
-        <v>72.38665749493896</v>
+        <v>71.72923765503151</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4695389925961775</v>
+        <v>-0.4691379216897804</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7470905863949516</v>
+        <v>0.7470902691271499</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6284900400926138</v>
+        <v>-0.6279534630238052</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645507198794973</v>
+        <v>0.7645497477023638</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143425878821521</v>
+        <v>1.143428077690494</v>
       </c>
     </row>
     <row r="19">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.98568459028793</v>
+        <v>2.989027969078697</v>
       </c>
       <c r="E19" t="n">
-        <v>95.22752247405863</v>
+        <v>97.73166700593708</v>
       </c>
       <c r="F19" t="n">
         <v>0.1243803563522274</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7177044716494189</v>
+        <v>0.7177070000035437</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926121887432273</v>
+        <v>0.6926171354791946</v>
       </c>
     </row>
     <row r="20">
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.598886914669237</v>
+        <v>2.59966114417101</v>
       </c>
       <c r="E20" t="n">
-        <v>103.1696258571254</v>
+        <v>102.7039509418933</v>
       </c>
       <c r="F20" t="n">
         <v>-0.3185046241899</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328106858180564</v>
+        <v>0.7328122288850969</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143879090235015</v>
+        <v>1.143885638928302</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-27.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-27.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>570.579593934408</v>
+        <v>572.9801017533337</v>
       </c>
       <c r="E2" t="n">
-        <v>13447.19293857713</v>
+        <v>13142.6538459252</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6285781031267437</v>
+        <v>0.6371767547450244</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4995396631555027</v>
+        <v>0.4995428248824025</v>
       </c>
       <c r="H2" t="n">
-        <v>1.258314703493469</v>
+        <v>1.275519781302078</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>225.7562054365478</v>
+        <v>226.6867896073241</v>
       </c>
       <c r="E3" t="n">
-        <v>5803.426972112772</v>
+        <v>5637.740002039078</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2664633371450289</v>
+        <v>0.2745676081090991</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5988653315633613</v>
+        <v>0.5988767016118215</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4449470074505999</v>
+        <v>0.4584710130985655</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907157771458715</v>
+        <v>0.8907184110096487</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067820712853246</v>
+        <v>1.067837385465312</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.53499833942598</v>
+        <v>37.86072026632871</v>
       </c>
       <c r="E4" t="n">
-        <v>1659.685841905225</v>
+        <v>1641.714116774049</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7879944128851699</v>
+        <v>0.8074389830466433</v>
       </c>
       <c r="G4" t="n">
-        <v>1.110611271801176</v>
+        <v>1.110568362730388</v>
       </c>
       <c r="H4" t="n">
-        <v>0.709514150353625</v>
+        <v>0.7270502295432894</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4735931938735952</v>
+        <v>0.4735723572316619</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052925279329825</v>
+        <v>1.052831611641999</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.81571636330064</v>
+        <v>37.34587635057682</v>
       </c>
       <c r="E5" t="n">
-        <v>412.2310482377949</v>
+        <v>452.5080383296016</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3418150205253144</v>
+        <v>-0.3302190387133348</v>
       </c>
       <c r="G5" t="n">
-        <v>0.562399024362785</v>
+        <v>0.5626597539405529</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6077802515973443</v>
+        <v>-0.5868893881260675</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7366252814563273</v>
+        <v>0.7364544635277473</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8293182106803783</v>
+        <v>0.8295050325955378</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.94851230730431</v>
+        <v>11.05443813419482</v>
       </c>
       <c r="E6" t="n">
-        <v>793.9444033352812</v>
+        <v>746.7297043479641</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4815045118533897</v>
+        <v>-0.4759173058781242</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8157119226341868</v>
+        <v>0.8158173606109748</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5902874513571682</v>
+        <v>-0.5833625623285393</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6679165529237313</v>
+        <v>0.667937091753907</v>
       </c>
       <c r="N6" t="n">
-        <v>1.09065913225596</v>
+        <v>1.090826748191452</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.76474957424572</v>
+        <v>10.94777275467462</v>
       </c>
       <c r="E7" t="n">
-        <v>209.3455376386929</v>
+        <v>213.7456262593283</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3126648121047451</v>
+        <v>-0.2965462231345982</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7156787418713688</v>
+        <v>0.7160421019261705</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.436878719196247</v>
+        <v>-0.4141463502451626</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7510756209958092</v>
+        <v>0.7508730889704951</v>
       </c>
       <c r="N7" t="n">
-        <v>1.076048400419426</v>
+        <v>1.0762976027787</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.01560502590497</v>
+        <v>10.18660515579428</v>
       </c>
       <c r="E8" t="n">
-        <v>708.8261935717513</v>
+        <v>727.1056920614355</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3107394264693449</v>
+        <v>-0.2948207685419456</v>
       </c>
       <c r="G8" t="n">
-        <v>1.17383821136373</v>
+        <v>1.173659941919158</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2647208307423705</v>
+        <v>-0.2511977771515804</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7375794500115088</v>
+        <v>0.737615202030788</v>
       </c>
       <c r="N8" t="n">
-        <v>1.733193590416938</v>
+        <v>1.73300340241688</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.381431692834557</v>
+        <v>7.402052436678042</v>
       </c>
       <c r="E9" t="n">
-        <v>228.7459746205541</v>
+        <v>228.0589149995538</v>
       </c>
       <c r="F9" t="n">
-        <v>0.430547595904863</v>
+        <v>0.4354997717080529</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4806872300078137</v>
+        <v>0.480680945560401</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8956917700889712</v>
+        <v>0.9060058979461445</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6788591717529852</v>
+        <v>0.6788488597777996</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6532392898975083</v>
+        <v>0.6532166924575676</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.738347546305466</v>
+        <v>6.829501409313234</v>
       </c>
       <c r="E10" t="n">
-        <v>328.6844861229803</v>
+        <v>331.0107754475987</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2607929625978147</v>
+        <v>-0.2460370226149222</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9600913652639883</v>
+        <v>0.9602360153669403</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2716334840967001</v>
+        <v>-0.2562255723358832</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7134856992717395</v>
+        <v>0.7134628536076272</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371285424630831</v>
+        <v>1.371439431287582</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.704634841271496</v>
+        <v>6.700454025519258</v>
       </c>
       <c r="E11" t="n">
-        <v>427.8507574637721</v>
+        <v>434.5571170349023</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9868503205903085</v>
+        <v>0.9850776798040384</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8229096335003813</v>
+        <v>0.8229058566017488</v>
       </c>
       <c r="H11" t="n">
-        <v>1.199220765459481</v>
+        <v>1.197072146104283</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.664285765062345</v>
+        <v>0.6643283708000025</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094301805814382</v>
+        <v>1.094360042438232</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.36140417359132</v>
+        <v>6.462415190958169</v>
       </c>
       <c r="E12" t="n">
-        <v>102.5917651306411</v>
+        <v>102.1697693404086</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2691755910505214</v>
+        <v>-0.2619942356774528</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6596166175198216</v>
+        <v>0.6597274941244748</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.408078850503539</v>
+        <v>-0.3971249311431923</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.788959819089503</v>
+        <v>0.7889500716460394</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041781154952792</v>
+        <v>1.041936802673316</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.73801618598084</v>
+        <v>4.818289981947166</v>
       </c>
       <c r="E13" t="n">
-        <v>247.6345177734999</v>
+        <v>269.5966767026844</v>
       </c>
       <c r="F13" t="n">
-        <v>1.768943632799012</v>
+        <v>1.824613483567873</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8623607194671514</v>
+        <v>0.862579196282984</v>
       </c>
       <c r="H13" t="n">
-        <v>2.051280389825772</v>
+        <v>2.115299663416966</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6039373501251989</v>
+        <v>0.6039089782035616</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042583574799999</v>
+        <v>1.042792119313366</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.587434979129345</v>
+        <v>4.608527167014825</v>
       </c>
       <c r="E14" t="n">
-        <v>119.6905854483058</v>
+        <v>118.2251366869567</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3994740487726847</v>
+        <v>-0.3945452424054273</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8517890897900607</v>
+        <v>0.8517999725926255</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4689823496930942</v>
+        <v>-0.4631900153794899</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,45 +1192,45 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601631113817611</v>
+        <v>0.7601683948927201</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296190658106541</v>
+        <v>1.296208023982389</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.267937873960314</v>
+        <v>4.311724050890019</v>
       </c>
       <c r="E15" t="n">
-        <v>382.9380166865365</v>
+        <v>306.2703232405728</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01193470458209456</v>
+        <v>0.610044609084659</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7947230630423694</v>
+        <v>0.9623022865370446</v>
       </c>
       <c r="H15" t="n">
-        <v>0.01501743832172929</v>
+        <v>0.633942803232833</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4268646717284502</v>
+        <v>0.3858131487889274</v>
       </c>
       <c r="J15" t="n">
         <v>269</v>
@@ -1246,45 +1246,45 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7153531921637969</v>
+        <v>0.5144081777734977</v>
       </c>
       <c r="N15" t="n">
-        <v>1.138063144860987</v>
+        <v>0.9909383961251435</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.211268284920711</v>
+        <v>4.30960476642298</v>
       </c>
       <c r="E16" t="n">
-        <v>287.6809616178132</v>
+        <v>395.7313079883542</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5659872612567243</v>
+        <v>0.0322565770071912</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9622222486421166</v>
+        <v>0.7954989833541096</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5882084539776988</v>
+        <v>0.04054886012699335</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3858131487889274</v>
+        <v>0.4268646717284502</v>
       </c>
       <c r="J16" t="n">
         <v>269</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5144065392530186</v>
+        <v>0.7150658529770793</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9908590917277523</v>
+        <v>1.138709497445821</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.394368641127036</v>
+        <v>3.43667062929362</v>
       </c>
       <c r="E17" t="n">
-        <v>79.34149493661023</v>
+        <v>85.91748834252114</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2054303509205885</v>
+        <v>-0.1920043445477075</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7546053101825909</v>
+        <v>0.7548618323185611</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2722354960249097</v>
+        <v>-0.2543569383525001</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7243996268447978</v>
+        <v>0.7243221356758264</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094279084183969</v>
+        <v>1.094527050115997</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.113087790752991</v>
+        <v>3.139015384956513</v>
       </c>
       <c r="E18" t="n">
-        <v>71.72923765503151</v>
+        <v>71.06932105414091</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4691379216897804</v>
+        <v>-0.463755892251099</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7470902691271499</v>
+        <v>0.7471395006619904</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6279534630238052</v>
+        <v>-0.6207085716123909</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645497477023638</v>
+        <v>0.7645540520625402</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143428077690494</v>
+        <v>1.143502627270406</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.989027969078697</v>
+        <v>3.002961730807971</v>
       </c>
       <c r="E19" t="n">
-        <v>97.73166700593708</v>
+        <v>100.3774594953696</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1243803563522274</v>
+        <v>0.1328072845130959</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4820765724053097</v>
+        <v>0.4821183709328297</v>
       </c>
       <c r="H19" t="n">
-        <v>0.258009543445836</v>
+        <v>0.2754661355387327</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7177070000035437</v>
+        <v>0.71770847306094</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926171354791946</v>
+        <v>0.6926742265155865</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.59966114417101</v>
+        <v>2.60749574734059</v>
       </c>
       <c r="E20" t="n">
-        <v>102.7039509418933</v>
+        <v>102.279714854839</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3185046241899</v>
+        <v>-0.3164804086327013</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7797580665759573</v>
+        <v>0.7797588901507588</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4084659560990563</v>
+        <v>-0.405869574082718</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328122288850969</v>
+        <v>0.7328120289603656</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143885638928302</v>
+        <v>1.143879295085017</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-27.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-27.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>572.9801017533337</v>
+        <v>574.1640339626151</v>
       </c>
       <c r="E2" t="n">
-        <v>13142.6538459252</v>
+        <v>13270.31307534754</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6371767547450244</v>
+        <v>0.6415982279587422</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4995428248824025</v>
+        <v>0.4995601979606222</v>
       </c>
       <c r="H2" t="n">
-        <v>1.275519781302078</v>
+        <v>1.284326154441384</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>226.6867896073241</v>
+        <v>226.9020043612231</v>
       </c>
       <c r="E3" t="n">
-        <v>5637.740002039078</v>
+        <v>5779.165964838251</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2745676081090991</v>
+        <v>0.2745124311049001</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5988767016118215</v>
+        <v>0.5988764566835822</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4584710130985655</v>
+        <v>0.4583790664022369</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907184110096487</v>
+        <v>0.8907178889585337</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067837385465312</v>
+        <v>1.067799187008519</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.86072026632871</v>
+        <v>37.71469076445248</v>
       </c>
       <c r="E4" t="n">
-        <v>1641.714116774049</v>
+        <v>1613.239411418819</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8074389830466433</v>
+        <v>0.7971981030018958</v>
       </c>
       <c r="G4" t="n">
-        <v>1.110568362730388</v>
+        <v>1.110581429536688</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7270502295432894</v>
+        <v>0.7178204873590136</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4735723572316619</v>
+        <v>0.4735050365287977</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052831611641999</v>
+        <v>1.052657722748411</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.34587635057682</v>
+        <v>37.27541398823283</v>
       </c>
       <c r="E5" t="n">
-        <v>452.5080383296016</v>
+        <v>474.906117171945</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3302190387133348</v>
+        <v>-0.3317182844246822</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5626597539405529</v>
+        <v>0.5626036309216523</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5868893881260675</v>
+        <v>-0.5896127685512165</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7364544635277473</v>
+        <v>0.7366105319327306</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8295050325955378</v>
+        <v>0.8295692121435793</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.05443813419482</v>
+        <v>11.13352594912856</v>
       </c>
       <c r="E6" t="n">
-        <v>746.7297043479641</v>
+        <v>698.6211715711074</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4759173058781242</v>
+        <v>-0.4708572914648923</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8158173606109748</v>
+        <v>0.8160018137427822</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5833625623285393</v>
+        <v>-0.5770297118644819</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.667937091753907</v>
+        <v>0.6679420995562548</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090826748191452</v>
+        <v>1.091043615840725</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.94777275467462</v>
+        <v>10.9124307481128</v>
       </c>
       <c r="E7" t="n">
-        <v>213.7456262593283</v>
+        <v>200.2036493049595</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2965462231345982</v>
+        <v>-0.3017270344874484</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7160421019261705</v>
+        <v>0.7158648390495483</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4141463502451626</v>
+        <v>-0.42148603762695</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7508730889704951</v>
+        <v>0.7510935742645014</v>
       </c>
       <c r="N7" t="n">
-        <v>1.0762976027787</v>
+        <v>1.076309687695315</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.18660515579428</v>
+        <v>10.24258194235338</v>
       </c>
       <c r="E8" t="n">
-        <v>727.1056920614355</v>
+        <v>748.5602442325348</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2948207685419456</v>
+        <v>-0.2898742475076268</v>
       </c>
       <c r="G8" t="n">
-        <v>1.173659941919158</v>
+        <v>1.17366910446243</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2511977771515804</v>
+        <v>-0.2469812372205167</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.737615202030788</v>
+        <v>0.7376291590491317</v>
       </c>
       <c r="N8" t="n">
-        <v>1.73300340241688</v>
+        <v>1.732989453645006</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.402052436678042</v>
+        <v>7.416836390266468</v>
       </c>
       <c r="E9" t="n">
-        <v>228.0589149995538</v>
+        <v>227.6261682131157</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4354997717080529</v>
+        <v>0.4395119702902697</v>
       </c>
       <c r="G9" t="n">
-        <v>0.480680945560401</v>
+        <v>0.4806890962993746</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9060058979461445</v>
+        <v>0.9143372996681004</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6788488597777996</v>
+        <v>0.6788668614849744</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6532166924575676</v>
+        <v>0.6532223733735639</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.829501409313234</v>
+        <v>6.816536328015423</v>
       </c>
       <c r="E10" t="n">
-        <v>331.0107754475987</v>
+        <v>335.9422368910953</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2460370226149222</v>
+        <v>-0.250778411555252</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9602360153669403</v>
+        <v>0.9601569206098959</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2562255723358832</v>
+        <v>-0.2611848190355765</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7134628536076272</v>
+        <v>0.7135213628206202</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371439431287582</v>
+        <v>1.371391230350231</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.700454025519258</v>
+        <v>6.714626109494938</v>
       </c>
       <c r="E11" t="n">
-        <v>434.5571170349023</v>
+        <v>466.7736727519956</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9850776798040384</v>
+        <v>0.9886233774372375</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8229058566017488</v>
+        <v>0.8229141230026527</v>
       </c>
       <c r="H11" t="n">
-        <v>1.197072146104283</v>
+        <v>1.201368830358561</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6643283708000025</v>
+        <v>0.6643375528622503</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094360042438232</v>
+        <v>1.094348102437216</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.462415190958169</v>
+        <v>6.564624624491628</v>
       </c>
       <c r="E12" t="n">
-        <v>102.1697693404086</v>
+        <v>108.5902358789592</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2619942356774528</v>
+        <v>-0.263507634130795</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6597274941244748</v>
+        <v>0.6596952703908098</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3971249311431923</v>
+        <v>-0.3994384164292865</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7889500716460394</v>
+        <v>0.7890253389129382</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041936802673316</v>
+        <v>1.041949071251671</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.818289981947166</v>
+        <v>4.798089686339572</v>
       </c>
       <c r="E13" t="n">
-        <v>269.5966767026844</v>
+        <v>286.6615449152293</v>
       </c>
       <c r="F13" t="n">
-        <v>1.824613483567873</v>
+        <v>1.806024499832596</v>
       </c>
       <c r="G13" t="n">
-        <v>0.862579196282984</v>
+        <v>0.8624682867620254</v>
       </c>
       <c r="H13" t="n">
-        <v>2.115299663416966</v>
+        <v>2.094018443985894</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6039089782035616</v>
+        <v>0.6040051829471286</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042792119313366</v>
+        <v>1.042787871128309</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.608527167014825</v>
+        <v>4.631799514943551</v>
       </c>
       <c r="E14" t="n">
-        <v>118.2251366869567</v>
+        <v>114.326863222332</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3945452424054273</v>
+        <v>-0.3920768707385018</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8517999725926255</v>
+        <v>0.8518268267566299</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4631900153794899</v>
+        <v>-0.4602776743148049</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601683948927201</v>
+        <v>0.7601843931724157</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296208023982389</v>
+        <v>1.296231088924775</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.311724050890019</v>
+        <v>4.420029104832615</v>
       </c>
       <c r="E15" t="n">
-        <v>306.2703232405728</v>
+        <v>358.1340448993056</v>
       </c>
       <c r="F15" t="n">
-        <v>0.610044609084659</v>
+        <v>0.6516385404497471</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9623022865370446</v>
+        <v>0.9629106389353878</v>
       </c>
       <c r="H15" t="n">
-        <v>0.633942803232833</v>
+        <v>0.6767383328220478</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5144081777734977</v>
+        <v>0.5143655440062176</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9909383961251435</v>
+        <v>0.9914481911235374</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.30960476642298</v>
+        <v>4.296780091600476</v>
       </c>
       <c r="E16" t="n">
-        <v>395.7313079883542</v>
+        <v>412.3492232089057</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0322565770071912</v>
+        <v>0.02043263710319421</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7954989833541096</v>
+        <v>0.7950013248757779</v>
       </c>
       <c r="H16" t="n">
-        <v>0.04054886012699335</v>
+        <v>0.02570138748685342</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7150658529770793</v>
+        <v>0.7156191250443806</v>
       </c>
       <c r="N16" t="n">
-        <v>1.138709497445821</v>
+        <v>1.138838031611103</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.43667062929362</v>
+        <v>3.436296361972488</v>
       </c>
       <c r="E17" t="n">
-        <v>85.91748834252114</v>
+        <v>89.41351797451199</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1920043445477075</v>
+        <v>-0.1929258194142559</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7548618323185611</v>
+        <v>0.7548354368823686</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2543569383525001</v>
+        <v>-0.2555865954188382</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7243221356758264</v>
+        <v>0.724435751963464</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094527050115997</v>
+        <v>1.094622388971134</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.139015384956513</v>
+        <v>3.14611459640697</v>
       </c>
       <c r="E18" t="n">
-        <v>71.06932105414091</v>
+        <v>70.27963253721933</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.463755892251099</v>
+        <v>-0.4617440193892388</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7471395006619904</v>
+        <v>0.7471833675736251</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6207085716123909</v>
+        <v>-0.6179795207282099</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645540520625402</v>
+        <v>0.7645780134602574</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143502627270406</v>
+        <v>1.14356583491269</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.002961730807971</v>
+        <v>2.990889868582873</v>
       </c>
       <c r="E19" t="n">
-        <v>100.3774594953696</v>
+        <v>104.8796387027975</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1328072845130959</v>
+        <v>0.1253158640769287</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4821183709328297</v>
+        <v>0.4820770374387753</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2754661355387327</v>
+        <v>0.2599498717937672</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.71770847306094</v>
+        <v>0.717690176735</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926742265155865</v>
+        <v>0.6925730985209355</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.60749574734059</v>
+        <v>2.610954827619914</v>
       </c>
       <c r="E20" t="n">
-        <v>102.279714854839</v>
+        <v>103.5058266522176</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3164804086327013</v>
+        <v>-0.3154677090028365</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7797588901507588</v>
+        <v>0.7797623768865077</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.405869574082718</v>
+        <v>-0.4045690307122268</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328120289603656</v>
+        <v>0.7328082140186822</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143879295085017</v>
+        <v>1.143838674694028</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-27.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-27.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>574.1640339626151</v>
+        <v>571.1513716283699</v>
       </c>
       <c r="E2" t="n">
-        <v>13270.31307534754</v>
+        <v>13084.78148622253</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6415982279587422</v>
+        <v>0.6315727943249065</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4995601979606222</v>
+        <v>0.499536166152845</v>
       </c>
       <c r="H2" t="n">
-        <v>1.284326154441384</v>
+        <v>1.264318456036798</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>226.9020043612231</v>
+        <v>225.7421260236375</v>
       </c>
       <c r="E3" t="n">
-        <v>5779.165964838251</v>
+        <v>5615.032624906277</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2745124311049001</v>
+        <v>0.2657472876724962</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5988764566835822</v>
+        <v>0.5988667135477336</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4583790664022369</v>
+        <v>0.4437503064716828</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907178889585337</v>
+        <v>0.8907127564970777</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067799187008519</v>
+        <v>1.067827031036698</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.71469076445248</v>
+        <v>37.57920817046399</v>
       </c>
       <c r="E4" t="n">
-        <v>1613.239411418819</v>
+        <v>1615.557331987106</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7971981030018958</v>
+        <v>0.7920834073677994</v>
       </c>
       <c r="G4" t="n">
-        <v>1.110581429536688</v>
+        <v>1.110595893776047</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7178204873590136</v>
+        <v>0.7132057770128257</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4735050365287977</v>
+        <v>0.4735742813762713</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052657722748411</v>
+        <v>1.052876023662124</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.27541398823283</v>
+        <v>37.05747762196749</v>
       </c>
       <c r="E5" t="n">
-        <v>474.906117171945</v>
+        <v>481.9317028458088</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3317182844246822</v>
+        <v>-0.3362107131052571</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5626036309216523</v>
+        <v>0.5624752170012571</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5896127685512165</v>
+        <v>-0.5977342697829576</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7366105319327306</v>
+        <v>0.7365347823484025</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8295692121435793</v>
+        <v>0.829334469856246</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.13352594912856</v>
+        <v>11.06865219994841</v>
       </c>
       <c r="E6" t="n">
-        <v>698.6211715711074</v>
+        <v>667.1156155723627</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4708572914648923</v>
+        <v>-0.4760075469720263</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8160018137427822</v>
+        <v>0.8158148362551593</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5770297118644819</v>
+        <v>-0.5834749820891308</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6679420995562548</v>
+        <v>0.6678478672642009</v>
       </c>
       <c r="N6" t="n">
-        <v>1.091043615840725</v>
+        <v>1.090692196866472</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.9124307481128</v>
+        <v>10.8048947975002</v>
       </c>
       <c r="E7" t="n">
-        <v>200.2036493049595</v>
+        <v>198.402435520763</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3017270344874484</v>
+        <v>-0.3102381226288967</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7158648390495483</v>
+        <v>0.7156978659372667</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.42148603762695</v>
+        <v>-0.4334763835331739</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7510935742645014</v>
+        <v>0.7510713081298875</v>
       </c>
       <c r="N7" t="n">
-        <v>1.076309687695315</v>
+        <v>1.076078508059011</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.24258194235338</v>
+        <v>10.27804639716111</v>
       </c>
       <c r="E8" t="n">
-        <v>748.5602442325348</v>
+        <v>672.6177831037384</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2898742475076268</v>
+        <v>-0.2811004880276768</v>
       </c>
       <c r="G8" t="n">
-        <v>1.17366910446243</v>
+        <v>1.173759825646063</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2469812372205167</v>
+        <v>-0.2394872288911005</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7376291590491317</v>
+        <v>0.737558868135671</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732989453645006</v>
+        <v>1.733041623660429</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.416836390266468</v>
+        <v>7.385667621254338</v>
       </c>
       <c r="E9" t="n">
-        <v>227.6261682131157</v>
+        <v>226.4812420493772</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4395119702902697</v>
+        <v>0.4303118903150678</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4806890962993746</v>
+        <v>0.4806879800970528</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9143372996681004</v>
+        <v>0.89520002191065</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6788668614849744</v>
+        <v>0.6788467476285112</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6532223733735639</v>
+        <v>0.653232926909159</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.816536328015423</v>
+        <v>6.761210085732722</v>
       </c>
       <c r="E10" t="n">
-        <v>335.9422368910953</v>
+        <v>313.7542432123337</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.250778411555252</v>
+        <v>-0.2573197061313606</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9601569206098959</v>
+        <v>0.9600984315178523</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2611848190355765</v>
+        <v>-0.2680138803315771</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7135213628206202</v>
+        <v>0.7134816759865733</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371391230350231</v>
+        <v>1.371297384345624</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.714626109494938</v>
+        <v>6.681651999443075</v>
       </c>
       <c r="E11" t="n">
-        <v>466.7736727519956</v>
+        <v>464.036998721981</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9886233774372375</v>
+        <v>0.9809431369723947</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8229141230026527</v>
+        <v>0.8228998151262953</v>
       </c>
       <c r="H11" t="n">
-        <v>1.201368830358561</v>
+        <v>1.192056577168927</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6643375528622503</v>
+        <v>0.6643173312479574</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094348102437216</v>
+        <v>1.094348409804371</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.564624624491628</v>
+        <v>6.353002872063062</v>
       </c>
       <c r="E12" t="n">
-        <v>108.5902358789592</v>
+        <v>107.5117191394262</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.263507634130795</v>
+        <v>-0.269553045068581</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6596952703908098</v>
+        <v>0.6596137427317257</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3994384164292865</v>
+        <v>-0.408652863950732</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890253389129382</v>
+        <v>0.7889906857042027</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041949071251671</v>
+        <v>1.041824665440905</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.798089686339572</v>
+        <v>4.762559688181716</v>
       </c>
       <c r="E13" t="n">
-        <v>286.6615449152293</v>
+        <v>290.3660551794976</v>
       </c>
       <c r="F13" t="n">
-        <v>1.806024499832596</v>
+        <v>1.784378224428822</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8624682867620254</v>
+        <v>0.8623870228453083</v>
       </c>
       <c r="H13" t="n">
-        <v>2.094018443985894</v>
+        <v>2.069115347470734</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6040051829471286</v>
+        <v>0.6039280801410495</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042787871128309</v>
+        <v>1.042606670617249</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.631799514943551</v>
+        <v>4.580796743545371</v>
       </c>
       <c r="E14" t="n">
-        <v>114.326863222332</v>
+        <v>114.590660715263</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3920768707385018</v>
+        <v>-0.4000894039158931</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8518268267566299</v>
+        <v>0.8517917444571083</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4602776743148049</v>
+        <v>-0.4697033124814929</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601843931724157</v>
+        <v>0.7601587921222731</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296231088924775</v>
+        <v>1.296196406744496</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.420029104832615</v>
+        <v>4.409823574268958</v>
       </c>
       <c r="E15" t="n">
-        <v>358.1340448993056</v>
+        <v>385.862155024776</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6516385404497471</v>
+        <v>0.6599907157074048</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9629106389353878</v>
+        <v>0.9630941706122557</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6767383328220478</v>
+        <v>0.6852816015777951</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5143655440062176</v>
+        <v>0.5138815151279121</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9914481911235374</v>
+        <v>0.9907516715289326</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.296780091600476</v>
+        <v>4.329441939815653</v>
       </c>
       <c r="E16" t="n">
-        <v>412.3492232089057</v>
+        <v>410.1054394756391</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02043263710319421</v>
+        <v>0.03260488179054644</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7950013248757779</v>
+        <v>0.7955155803440179</v>
       </c>
       <c r="H16" t="n">
-        <v>0.02570138748685342</v>
+        <v>0.04098584942415153</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7156191250443806</v>
+        <v>0.7147354513509655</v>
       </c>
       <c r="N16" t="n">
-        <v>1.138838031611103</v>
+        <v>1.138222266773644</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.436296361972488</v>
+        <v>3.396884235769931</v>
       </c>
       <c r="E17" t="n">
-        <v>89.41351797451199</v>
+        <v>85.47478070510562</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1929258194142559</v>
+        <v>-0.2061643100947042</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7548354368823686</v>
+        <v>0.7545992515650651</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2555865954188382</v>
+        <v>-0.2732103294127475</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.724435751963464</v>
+        <v>0.724436860707759</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094622388971134</v>
+        <v>1.09433420428053</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.14611459640697</v>
+        <v>3.127984968063155</v>
       </c>
       <c r="E18" t="n">
-        <v>70.27963253721933</v>
+        <v>69.63328403815936</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4617440193892388</v>
+        <v>-0.4664085270175843</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7471833675736251</v>
+        <v>0.7471028131982849</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6179795207282099</v>
+        <v>-0.6242896141977143</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645780134602574</v>
+        <v>0.764538189037308</v>
       </c>
       <c r="N18" t="n">
-        <v>1.14356583491269</v>
+        <v>1.143437994142202</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.990889868582873</v>
+        <v>2.971345513664451</v>
       </c>
       <c r="E19" t="n">
-        <v>104.8796387027975</v>
+        <v>106.9771363945011</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1253158640769287</v>
+        <v>0.1159700069133303</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4820770374387753</v>
+        <v>0.4821194039948284</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2599498717937672</v>
+        <v>0.2405420855340107</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.717690176735</v>
+        <v>0.7176567811156417</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6925730985209355</v>
+        <v>0.6926350543324916</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.610954827619914</v>
+        <v>2.594783650148485</v>
       </c>
       <c r="E20" t="n">
-        <v>103.5058266522176</v>
+        <v>102.9507786559989</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3154677090028365</v>
+        <v>-0.3205272596265031</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7797623768865077</v>
+        <v>0.7797654428581223</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4045690307122268</v>
+        <v>-0.4110559945458147</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328082140186822</v>
+        <v>0.7328085082130792</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143838674694028</v>
+        <v>1.143898659706117</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-27.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-27.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>571.1513716283699</v>
+        <v>567.3935259255014</v>
       </c>
       <c r="E2" t="n">
-        <v>13084.78148622253</v>
+        <v>13057.39702395564</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6315727943249065</v>
+        <v>0.6155492396928803</v>
       </c>
       <c r="G2" t="n">
-        <v>0.499536166152845</v>
+        <v>0.4996122730175458</v>
       </c>
       <c r="H2" t="n">
-        <v>1.264318456036798</v>
+        <v>1.232053880452338</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>225.7421260236375</v>
+        <v>224.6714720577153</v>
       </c>
       <c r="E3" t="n">
-        <v>5615.032624906277</v>
+        <v>5303.019130348038</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2657472876724962</v>
+        <v>0.2566499093791261</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5988667135477336</v>
+        <v>0.5989181307128826</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4437503064716828</v>
+        <v>0.4285225245621466</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907127564970777</v>
+        <v>0.8907343345018326</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067827031036698</v>
+        <v>1.06778190087193</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.57920817046399</v>
+        <v>37.79412664513924</v>
       </c>
       <c r="E4" t="n">
-        <v>1615.557331987106</v>
+        <v>1749.516681317793</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7920834073677994</v>
+        <v>0.805389582998794</v>
       </c>
       <c r="G4" t="n">
-        <v>1.110595893776047</v>
+        <v>1.110569284146715</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7132057770128257</v>
+        <v>0.7252042664025238</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4735742813762713</v>
+        <v>0.473533038407386</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052876023662124</v>
+        <v>1.052598736831752</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.05747762196749</v>
+        <v>36.97819321476906</v>
       </c>
       <c r="E5" t="n">
-        <v>481.9317028458088</v>
+        <v>485.525912939777</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3362107131052571</v>
+        <v>-0.338827611771038</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5624752170012571</v>
+        <v>0.5624279978955736</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5977342697829576</v>
+        <v>-0.6024373129339631</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7365347823484025</v>
+        <v>0.7363048181104298</v>
       </c>
       <c r="N5" t="n">
-        <v>0.829334469856246</v>
+        <v>0.8288796473904275</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.06865219994841</v>
+        <v>10.95515213041273</v>
       </c>
       <c r="E6" t="n">
-        <v>667.1156155723627</v>
+        <v>599.9353511513932</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4760075469720263</v>
+        <v>-0.4831236498236517</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8158148362551593</v>
+        <v>0.8157007603129999</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5834749820891308</v>
+        <v>-0.5922804946733996</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6678478672642009</v>
+        <v>0.6678063582794416</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090692196866472</v>
+        <v>1.090305790328865</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.8048947975002</v>
+        <v>10.76784686760569</v>
       </c>
       <c r="E7" t="n">
-        <v>198.402435520763</v>
+        <v>190.6960538267697</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3102381226288967</v>
+        <v>-0.3138773128361451</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7156978659372667</v>
+        <v>0.7156739445482591</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4334763835331739</v>
+        <v>-0.438575855984624</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7510713081298875</v>
+        <v>0.7509504155978268</v>
       </c>
       <c r="N7" t="n">
-        <v>1.076078508059011</v>
+        <v>1.075705452240115</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.27804639716111</v>
+        <v>10.11728644839067</v>
       </c>
       <c r="E8" t="n">
-        <v>672.6177831037384</v>
+        <v>631.0928655202605</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2811004880276768</v>
+        <v>-0.3008962862864404</v>
       </c>
       <c r="G8" t="n">
-        <v>1.173759825646063</v>
+        <v>1.173690421522554</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2394872288911005</v>
+        <v>-0.2563676764918187</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.737558868135671</v>
+        <v>0.7376258965897311</v>
       </c>
       <c r="N8" t="n">
-        <v>1.733041623660429</v>
+        <v>1.732832630922877</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.385667621254338</v>
+        <v>7.3911034623464</v>
       </c>
       <c r="E9" t="n">
-        <v>226.4812420493772</v>
+        <v>222.1613593930552</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4303118903150678</v>
+        <v>0.433612697839024</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4806879800970528</v>
+        <v>0.4806812084157057</v>
       </c>
       <c r="H9" t="n">
-        <v>0.89520002191065</v>
+        <v>0.9020795700921689</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6788467476285112</v>
+        <v>0.6787737547515093</v>
       </c>
       <c r="N9" t="n">
-        <v>0.653232926909159</v>
+        <v>0.6530539906559959</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.761210085732722</v>
+        <v>6.701525682527528</v>
       </c>
       <c r="E10" t="n">
-        <v>313.7542432123337</v>
+        <v>263.4073607227371</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2573197061313606</v>
+        <v>-0.2656483173966394</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9600984315178523</v>
+        <v>0.9601095261023351</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2680138803315771</v>
+        <v>-0.2766854303332105</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7134816759865733</v>
+        <v>0.7134748712435522</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371297384345624</v>
+        <v>1.371091259184328</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.681651999443075</v>
+        <v>6.643086554979027</v>
       </c>
       <c r="E11" t="n">
-        <v>464.036998721981</v>
+        <v>451.2704913820315</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9809431369723947</v>
+        <v>0.9617767961713561</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8228998151262953</v>
+        <v>0.8229225895943061</v>
       </c>
       <c r="H11" t="n">
-        <v>1.192056577168927</v>
+        <v>1.168733011261125</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6643173312479574</v>
+        <v>0.6643352620154995</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094348409804371</v>
+        <v>1.094241522280233</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.353002872063062</v>
+        <v>6.45703484677807</v>
       </c>
       <c r="E12" t="n">
-        <v>107.5117191394262</v>
+        <v>105.0508953461337</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.269553045068581</v>
+        <v>-0.2776558791102879</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6596137427317257</v>
+        <v>0.6596235618050723</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.408652863950732</v>
+        <v>-0.420930808399987</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7889906857042027</v>
+        <v>0.7890066948154892</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041824665440905</v>
+        <v>1.041702605059831</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.762559688181716</v>
+        <v>4.727929518449163</v>
       </c>
       <c r="E13" t="n">
-        <v>290.3660551794976</v>
+        <v>244.4398785551978</v>
       </c>
       <c r="F13" t="n">
-        <v>1.784378224428822</v>
+        <v>1.758152859358115</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8623870228453083</v>
+        <v>0.8623580477313738</v>
       </c>
       <c r="H13" t="n">
-        <v>2.069115347470734</v>
+        <v>2.038773643944451</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6039280801410495</v>
+        <v>0.6038817533392958</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042606670617249</v>
+        <v>1.04233286089028</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.580796743545371</v>
+        <v>4.549828656115773</v>
       </c>
       <c r="E14" t="n">
-        <v>114.590660715263</v>
+        <v>110.0011348295757</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4000894039158931</v>
+        <v>-0.4056201219010011</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8517917444571083</v>
+        <v>0.8518557841927934</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4697033124814929</v>
+        <v>-0.4761605537319454</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601587921222731</v>
+        <v>0.7602064990921459</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296196406744496</v>
+        <v>1.296177733027498</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.409823574268958</v>
+        <v>4.348095996050649</v>
       </c>
       <c r="E15" t="n">
-        <v>385.862155024776</v>
+        <v>409.8634041081786</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6599907157074048</v>
+        <v>0.6266486852033786</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9630941706122557</v>
+        <v>0.9624837310429676</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6852816015777951</v>
+        <v>0.6510745740339204</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5138815151279121</v>
+        <v>0.513721588724129</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9907516715289326</v>
+        <v>0.9896647823444401</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.329441939815653</v>
+        <v>4.279708215159426</v>
       </c>
       <c r="E16" t="n">
-        <v>410.1054394756391</v>
+        <v>421.1844473366605</v>
       </c>
       <c r="F16" t="n">
-        <v>0.03260488179054644</v>
+        <v>0.01713530209898506</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7955155803440179</v>
+        <v>0.794885433611372</v>
       </c>
       <c r="H16" t="n">
-        <v>0.04098584942415153</v>
+        <v>0.0215569456608796</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7147354513509655</v>
+        <v>0.7145481689963278</v>
       </c>
       <c r="N16" t="n">
-        <v>1.138222266773644</v>
+        <v>1.13684943670091</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.396884235769931</v>
+        <v>3.373053751254745</v>
       </c>
       <c r="E17" t="n">
-        <v>85.47478070510562</v>
+        <v>82.24955887021345</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2061643100947042</v>
+        <v>-0.2116633107959228</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7545992515650651</v>
+        <v>0.754580304581335</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2732103294127475</v>
+        <v>-0.2805046852016106</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.724436860707759</v>
+        <v>0.724362436522467</v>
       </c>
       <c r="N17" t="n">
-        <v>1.09433420428053</v>
+        <v>1.094027624015565</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.127984968063155</v>
+        <v>3.090029975917301</v>
       </c>
       <c r="E18" t="n">
-        <v>69.63328403815936</v>
+        <v>64.6153322846891</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4664085270175843</v>
+        <v>-0.47514559945323</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7471028131982849</v>
+        <v>0.7471532331761237</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6242896141977143</v>
+        <v>-0.635941301402661</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.764538189037308</v>
+        <v>0.7646007322193201</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143437994142202</v>
+        <v>1.143434499148971</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.971345513664451</v>
+        <v>2.964512827395568</v>
       </c>
       <c r="E19" t="n">
-        <v>106.9771363945011</v>
+        <v>109.6936745511158</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1159700069133303</v>
+        <v>0.1131702514606543</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4821194039948284</v>
+        <v>0.4821524852695104</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2405420855340107</v>
+        <v>0.2347187973061989</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7176567811156417</v>
+        <v>0.7177993405206868</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926350543324916</v>
+        <v>0.6927146402280447</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.594783650148485</v>
+        <v>2.580072809136309</v>
       </c>
       <c r="E20" t="n">
-        <v>102.9507786559989</v>
+        <v>99.91210085478237</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3205272596265031</v>
+        <v>-0.3250724004913008</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7797654428581223</v>
+        <v>0.7798120185960785</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4110559945458147</v>
+        <v>-0.4168599518080517</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328085082130792</v>
+        <v>0.7328568122595703</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143898659706117</v>
+        <v>1.143868117286928</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-27.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-27.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>567.3935259255014</v>
+        <v>566.7543956381148</v>
       </c>
       <c r="E2" t="n">
-        <v>13057.39702395564</v>
+        <v>12150.42599787189</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6155492396928803</v>
+        <v>0.6142482439073838</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4996122730175458</v>
+        <v>0.4996246623845079</v>
       </c>
       <c r="H2" t="n">
-        <v>1.232053880452338</v>
+        <v>1.229419382493697</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>224.6714720577153</v>
+        <v>224.4738867160829</v>
       </c>
       <c r="E3" t="n">
-        <v>5303.019130348038</v>
+        <v>4752.531634631231</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2566499093791261</v>
+        <v>0.2564758337917135</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5989181307128826</v>
+        <v>0.5989197278880729</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4285225245621466</v>
+        <v>0.4282307325158675</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907343345018326</v>
+        <v>0.8907320147531218</v>
       </c>
       <c r="N3" t="n">
-        <v>1.06778190087193</v>
+        <v>1.067755489392904</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.79412664513924</v>
+        <v>37.41586890158406</v>
       </c>
       <c r="E4" t="n">
-        <v>1749.516681317793</v>
+        <v>1661.50823129493</v>
       </c>
       <c r="F4" t="n">
-        <v>0.805389582998794</v>
+        <v>0.7730224830986472</v>
       </c>
       <c r="G4" t="n">
-        <v>1.110569284146715</v>
+        <v>1.110696604420446</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7252042664025238</v>
+        <v>0.695979874271791</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.473533038407386</v>
+        <v>0.4737291268346409</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052598736831752</v>
+        <v>1.053129223203481</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.97819321476906</v>
+        <v>36.9507941333679</v>
       </c>
       <c r="E5" t="n">
-        <v>485.525912939777</v>
+        <v>469.9680758349004</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.338827611771038</v>
+        <v>-0.3384539355995143</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5624279978955736</v>
+        <v>0.5624334940298592</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6024373129339631</v>
+        <v>-0.6017670341331877</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7363048181104298</v>
+        <v>0.7362482314174275</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8288796473904275</v>
+        <v>0.8288034927922081</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.95515213041273</v>
+        <v>10.80965676200265</v>
       </c>
       <c r="E6" t="n">
-        <v>599.9353511513932</v>
+        <v>557.6416749835051</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4831236498236517</v>
+        <v>-0.4945095744468783</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8157007603129999</v>
+        <v>0.81587072918156</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5922804946733996</v>
+        <v>-0.6061126557916168</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6678063582794416</v>
+        <v>0.6680823784762199</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090305790328865</v>
+        <v>1.090956668710767</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.76784686760569</v>
+        <v>10.75316654170913</v>
       </c>
       <c r="E7" t="n">
-        <v>190.6960538267697</v>
+        <v>179.2976644270868</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3138773128361451</v>
+        <v>-0.3147863187455656</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7156739445482591</v>
+        <v>0.7156724311797238</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.438575855984624</v>
+        <v>-0.439846925815862</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7509504155978268</v>
+        <v>0.7509602310924179</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075705452240115</v>
+        <v>1.075690562872147</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.11728644839067</v>
+        <v>10.07651338412151</v>
       </c>
       <c r="E8" t="n">
-        <v>631.0928655202605</v>
+        <v>540.0228744280648</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3008962862864404</v>
+        <v>-0.3050651710419703</v>
       </c>
       <c r="G8" t="n">
-        <v>1.173690421522554</v>
+        <v>1.173738102407423</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2563676764918187</v>
+        <v>-0.2599090635434423</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7376258965897311</v>
+        <v>0.7376687023641548</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732832630922877</v>
+        <v>1.732960616447536</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.3911034623464</v>
+        <v>7.3852725501546</v>
       </c>
       <c r="E9" t="n">
-        <v>222.1613593930552</v>
+        <v>215.2367332826409</v>
       </c>
       <c r="F9" t="n">
-        <v>0.433612697839024</v>
+        <v>0.4329052134914253</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4806812084157057</v>
+        <v>0.4806819832428351</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9020795700921689</v>
+        <v>0.9006062814564167</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6787737547515093</v>
+        <v>0.6787742417307008</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6530539906559959</v>
+        <v>0.6530393178192753</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.701525682527528</v>
+        <v>6.672224032373077</v>
       </c>
       <c r="E10" t="n">
-        <v>263.4073607227371</v>
+        <v>249.4704455491394</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2656483173966394</v>
+        <v>-0.2707719555075664</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9601095261023351</v>
+        <v>0.9601643105367005</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2766854303332105</v>
+        <v>-0.2820058530984282</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7134748712435522</v>
+        <v>0.7135411154775143</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371091259184328</v>
+        <v>1.371262799382778</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.643086554979027</v>
+        <v>6.620050735582765</v>
       </c>
       <c r="E11" t="n">
-        <v>451.2704913820315</v>
+        <v>437.3494725612097</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9617767961713561</v>
+        <v>0.9511827154887678</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8229225895943061</v>
+        <v>0.8229711885095559</v>
       </c>
       <c r="H11" t="n">
-        <v>1.168733011261125</v>
+        <v>1.155791027400862</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6643352620154995</v>
+        <v>0.6643953375912216</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094241522280233</v>
+        <v>1.094377963665969</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.45703484677807</v>
+        <v>6.297244151776185</v>
       </c>
       <c r="E12" t="n">
-        <v>105.0508953461337</v>
+        <v>101.3973610718852</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2776558791102879</v>
+        <v>-0.2787846149782552</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6596235618050723</v>
+        <v>0.6596358145185613</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.420930808399987</v>
+        <v>-0.4226341396907438</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890066948154892</v>
+        <v>0.7890215806910384</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041702605059831</v>
+        <v>1.041715776334732</v>
       </c>
     </row>
     <row r="13">
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.727929518449163</v>
+        <v>4.728330951162167</v>
       </c>
       <c r="E13" t="n">
-        <v>244.4398785551978</v>
+        <v>234.0717369187682</v>
       </c>
       <c r="F13" t="n">
         <v>1.758152859358115</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6038817533392958</v>
+        <v>0.6038683355306858</v>
       </c>
       <c r="N13" t="n">
-        <v>1.04233286089028</v>
+        <v>1.042283854503303</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.549828656115773</v>
+        <v>4.537025055393788</v>
       </c>
       <c r="E14" t="n">
-        <v>110.0011348295757</v>
+        <v>103.8583606717352</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4056201219010011</v>
+        <v>-0.4074606969089124</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8518557841927934</v>
+        <v>0.8518931880111806</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4761605537319454</v>
+        <v>-0.4783002172609986</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7602064990921459</v>
+        <v>0.7602295289208979</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296177733027498</v>
+        <v>1.296241770615892</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.348095996050649</v>
+        <v>4.282764079108114</v>
       </c>
       <c r="E15" t="n">
-        <v>409.8634041081786</v>
+        <v>400.5274885431994</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6266486852033786</v>
+        <v>0.5948636578259374</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9624837310429676</v>
+        <v>0.9622085113015718</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6510745740339204</v>
+        <v>0.6182273912972045</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.513721588724129</v>
+        <v>0.5141561097668703</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9896647823444401</v>
+        <v>0.990194084083564</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.279708215159426</v>
+        <v>4.278900696718301</v>
       </c>
       <c r="E16" t="n">
-        <v>421.1844473366605</v>
+        <v>376.8606845256498</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01713530209898506</v>
+        <v>0.01488084901685882</v>
       </c>
       <c r="G16" t="n">
-        <v>0.794885433611372</v>
+        <v>0.7948119729667835</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0215569456608796</v>
+        <v>0.01872247716817008</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7145481689963278</v>
+        <v>0.7145891758007333</v>
       </c>
       <c r="N16" t="n">
-        <v>1.13684943670091</v>
+        <v>1.136781419012073</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.373053751254745</v>
+        <v>3.373313133789545</v>
       </c>
       <c r="E17" t="n">
-        <v>82.24955887021345</v>
+        <v>79.56467904193046</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2116633107959228</v>
+        <v>-0.2114801728309345</v>
       </c>
       <c r="G17" t="n">
-        <v>0.754580304581335</v>
+        <v>0.7545801829021793</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2805046852016106</v>
+        <v>-0.2802620286389761</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.724362436522467</v>
+        <v>0.7243406687231791</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094027624015565</v>
+        <v>1.09396744284009</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.090029975917301</v>
+        <v>3.081345366184801</v>
       </c>
       <c r="E18" t="n">
-        <v>64.6153322846891</v>
+        <v>61.90059019051685</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.47514559945323</v>
+        <v>-0.4765847625820528</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7471532331761237</v>
+        <v>0.7471869015243595</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.635941301402661</v>
+        <v>-0.6378387544130623</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7646007322193201</v>
+        <v>0.7646234496608044</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143434499148971</v>
+        <v>1.143491643223252</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.964512827395568</v>
+        <v>2.969389276881271</v>
       </c>
       <c r="E19" t="n">
-        <v>109.6936745511158</v>
+        <v>106.8133079499891</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1131702514606543</v>
+        <v>0.1159700069133303</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4821524852695104</v>
+        <v>0.4821194039948284</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2347187973061989</v>
+        <v>0.2405420855340107</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7177993405206868</v>
+        <v>0.7177718700310209</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6927146402280447</v>
+        <v>0.6926234276187314</v>
       </c>
     </row>
     <row r="20">
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.580072809136309</v>
+        <v>2.581515527493141</v>
       </c>
       <c r="E20" t="n">
-        <v>99.91210085478237</v>
+        <v>95.11515012439514</v>
       </c>
       <c r="F20" t="n">
         <v>-0.3250724004913008</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328568122595703</v>
+        <v>0.7328548081219599</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143868117286928</v>
+        <v>1.14383662434104</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-27.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-27.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>566.7543956381148</v>
+        <v>567.0354374238499</v>
       </c>
       <c r="E2" t="n">
-        <v>12150.42599787189</v>
+        <v>11357.84402063325</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6142482439073838</v>
+        <v>0.6159984927821276</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4996246623845079</v>
+        <v>0.4996082119316904</v>
       </c>
       <c r="H2" t="n">
-        <v>1.229419382493697</v>
+        <v>1.232963106031473</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>224.4738867160829</v>
+        <v>224.1634445805299</v>
       </c>
       <c r="E3" t="n">
-        <v>4752.531634631231</v>
+        <v>4538.566235136278</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2564758337917135</v>
+        <v>0.2551750486961621</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5989197278880729</v>
+        <v>0.5989323933980563</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4282307325158675</v>
+        <v>0.426049837191842</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907320147531218</v>
+        <v>0.8907422240905781</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067755489392904</v>
+        <v>1.067825466904496</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.41586890158406</v>
+        <v>37.55065686428311</v>
       </c>
       <c r="E4" t="n">
-        <v>1661.50823129493</v>
+        <v>1531.717640760137</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7730224830986472</v>
+        <v>0.7920834073677994</v>
       </c>
       <c r="G4" t="n">
-        <v>1.110696604420446</v>
+        <v>1.110595893776047</v>
       </c>
       <c r="H4" t="n">
-        <v>0.695979874271791</v>
+        <v>0.7132057770128257</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4737291268346409</v>
+        <v>0.4736212988405912</v>
       </c>
       <c r="N4" t="n">
-        <v>1.053129223203481</v>
+        <v>1.052828710848246</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.9507941333679</v>
+        <v>36.95369260825237</v>
       </c>
       <c r="E5" t="n">
-        <v>469.9680758349004</v>
+        <v>436.2546970033501</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3384539355995143</v>
+        <v>-0.3377064167020573</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5624334940298592</v>
+        <v>0.5624457358078357</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6017670341331877</v>
+        <v>-0.6004248858194516</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7362482314174275</v>
+        <v>0.7362488586050036</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8288034927922081</v>
+        <v>0.8288495287431119</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.80965676200265</v>
+        <v>10.85141785782871</v>
       </c>
       <c r="E6" t="n">
-        <v>557.6416749835051</v>
+        <v>543.9867438329713</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4945095744468783</v>
+        <v>-0.4886008042270009</v>
       </c>
       <c r="G6" t="n">
-        <v>0.81587072918156</v>
+        <v>0.8157280251285697</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6061126557916168</v>
+        <v>-0.5989751353093341</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6680823784762199</v>
+        <v>0.6679793209402939</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090956668710767</v>
+        <v>1.090633498978295</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.75316654170913</v>
+        <v>10.75669350030339</v>
       </c>
       <c r="E7" t="n">
-        <v>179.2976644270868</v>
+        <v>173.3321138519329</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3147863187455656</v>
+        <v>-0.3132711328533401</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7156724311797238</v>
+        <v>0.7156759461412533</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.439846925815862</v>
+        <v>-0.4377276259491745</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7509602310924179</v>
+        <v>0.7509375211281487</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075690562872147</v>
+        <v>1.075698733710637</v>
       </c>
     </row>
     <row r="8">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.07651338412151</v>
+        <v>10.05705242244095</v>
       </c>
       <c r="E8" t="n">
-        <v>540.0228744280648</v>
+        <v>525.4509202257043</v>
       </c>
       <c r="F8" t="n">
         <v>-0.3050651710419703</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7376687023641548</v>
+        <v>0.7376716980516886</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732960616447536</v>
+        <v>1.733024714952509</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.3852725501546</v>
+        <v>7.390808972711061</v>
       </c>
       <c r="E9" t="n">
-        <v>215.2367332826409</v>
+        <v>210.4031078730446</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4329052134914253</v>
+        <v>0.434084405094858</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4806819832428351</v>
+        <v>0.4806808967901449</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9006062814564167</v>
+        <v>0.9030614863073497</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6787742417307008</v>
+        <v>0.6787691257236839</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6530393178192753</v>
+        <v>0.6530544219936339</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.672224032373077</v>
+        <v>6.655828437306068</v>
       </c>
       <c r="E10" t="n">
-        <v>249.4704455491394</v>
+        <v>243.7179680207244</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2707719555075664</v>
+        <v>-0.2722933781692652</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9601643105367005</v>
+        <v>0.9601876500441239</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2820058530984282</v>
+        <v>-0.283583503866929</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7135411154775143</v>
+        <v>0.7135557840606627</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371262799382778</v>
+        <v>1.371369475340564</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.620050735582765</v>
+        <v>6.613684762381808</v>
       </c>
       <c r="E11" t="n">
-        <v>437.3494725612097</v>
+        <v>420.7974845000215</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9511827154887678</v>
+        <v>0.9544181946645596</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8229711885095559</v>
+        <v>0.8229536174655825</v>
       </c>
       <c r="H11" t="n">
-        <v>1.155791027400862</v>
+        <v>1.159747249916518</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6643953375912216</v>
+        <v>0.6643778345101429</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094377963665969</v>
+        <v>1.094361800339718</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.297244151776185</v>
+        <v>6.308239008189903</v>
       </c>
       <c r="E12" t="n">
-        <v>101.3973610718852</v>
+        <v>99.13392614165797</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2787846149782552</v>
+        <v>-0.275020357903636</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6596358145185613</v>
+        <v>0.6596053361317308</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4226341396907438</v>
+        <v>-0.416946835992108</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890215806910384</v>
+        <v>0.7889513126921525</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041715776334732</v>
+        <v>1.041609171690375</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.728330951162167</v>
+        <v>4.739105874481876</v>
       </c>
       <c r="E13" t="n">
-        <v>234.0717369187682</v>
+        <v>227.9945074172246</v>
       </c>
       <c r="F13" t="n">
-        <v>1.758152859358115</v>
+        <v>1.770486076153826</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8623580477313738</v>
+        <v>0.8623621593545951</v>
       </c>
       <c r="H13" t="n">
-        <v>2.038773643944451</v>
+        <v>2.053065590770918</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6038683355306858</v>
+        <v>0.6038079409118144</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042283854503303</v>
+        <v>1.042218897377446</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.537025055393788</v>
+        <v>4.543338156590035</v>
       </c>
       <c r="E14" t="n">
-        <v>103.8583606717352</v>
+        <v>95.80977718077993</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4074606969089124</v>
+        <v>-0.4050062633915278</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8518931880111806</v>
+        <v>0.8518451002307604</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4783002172609986</v>
+        <v>-0.4754459035824866</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7602295289208979</v>
+        <v>0.7601987977603226</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296241770615892</v>
+        <v>1.296158881315557</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.282764079108114</v>
+        <v>4.296864729894082</v>
       </c>
       <c r="E15" t="n">
-        <v>400.5274885431994</v>
+        <v>345.3987701915138</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5948636578259374</v>
+        <v>0.6072816239470944</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9622085113015718</v>
+        <v>0.9622800740464837</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6182273912972045</v>
+        <v>0.6310861466697679</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5141561097668703</v>
+        <v>0.5140299858987374</v>
       </c>
       <c r="N15" t="n">
-        <v>0.990194084083564</v>
+        <v>0.9900574111467575</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.278900696718301</v>
+        <v>4.261474333984061</v>
       </c>
       <c r="E16" t="n">
-        <v>376.8606845256498</v>
+        <v>367.0257341882715</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01488084901685882</v>
+        <v>0.010029576861319</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7948119729667835</v>
+        <v>0.7946698547123576</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01872247716817008</v>
+        <v>0.01262106118892525</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7145891758007333</v>
+        <v>0.7148972629880364</v>
       </c>
       <c r="N16" t="n">
-        <v>1.136781419012073</v>
+        <v>1.137105617052268</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.373313133789545</v>
+        <v>3.382026757956081</v>
       </c>
       <c r="E17" t="n">
-        <v>79.56467904193046</v>
+        <v>77.08818479394857</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2114801728309345</v>
+        <v>-0.2072649142612236</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7545801829021793</v>
+        <v>0.7545917219804916</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2802620286389761</v>
+        <v>-0.2746715981951655</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7243406687231791</v>
+        <v>0.7242499945764914</v>
       </c>
       <c r="N17" t="n">
-        <v>1.09396744284009</v>
+        <v>1.09388324190828</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.081345366184801</v>
+        <v>3.082939082430074</v>
       </c>
       <c r="E18" t="n">
-        <v>61.90059019051685</v>
+        <v>59.57842145501015</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4765847625820528</v>
+        <v>-0.4745056379188235</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7471869015243595</v>
+        <v>0.7471405749600911</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6378387544130623</v>
+        <v>-0.6350955279656301</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7646234496608044</v>
+        <v>0.7645903552681154</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143491643223252</v>
+        <v>1.14340890321888</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.969389276881271</v>
+        <v>2.971159995289557</v>
       </c>
       <c r="E19" t="n">
-        <v>106.8133079499891</v>
+        <v>107.7515545590224</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1159700069133303</v>
+        <v>0.117837537707888</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4821194039948284</v>
+        <v>0.4821025726077462</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2405420855340107</v>
+        <v>0.244424204315052</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7177718700310209</v>
+        <v>0.7177460245020374</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926234276187314</v>
+        <v>0.6925971123523602</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.581515527493141</v>
+        <v>2.592028262757619</v>
       </c>
       <c r="E20" t="n">
-        <v>95.11515012439514</v>
+        <v>91.53524822876388</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3250724004913008</v>
+        <v>-0.3200217490253464</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7798120185960785</v>
+        <v>0.7797628300592955</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4168599518080517</v>
+        <v>-0.4104090842609297</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328548081219599</v>
+        <v>0.7327656382134816</v>
       </c>
       <c r="N20" t="n">
-        <v>1.14383662434104</v>
+        <v>1.14366296265297</v>
       </c>
     </row>
   </sheetData>
